--- a/DBC/DBC Files.xlsx
+++ b/DBC/DBC Files.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\wow-server\Zeppelin-Craft\DBC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686D1DC4-DF3E-4F13-9D8B-2E0CE2D9A591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D643F1BD-C2A4-46B3-BBC7-47F1709CC0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1668" yWindow="2052" windowWidth="22020" windowHeight="18516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2304" yWindow="2304" windowWidth="22020" windowHeight="18516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DBC Files" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="94">
   <si>
     <t>DBC</t>
   </si>
@@ -902,13 +902,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:K79" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:K79" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="x"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K79" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K79">
     <sortCondition ref="A1:A79"/>
   </sortState>
@@ -1355,7 +1349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>66</v>
       </c>
@@ -1368,7 +1362,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="28.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>70</v>
       </c>
@@ -1381,7 +1375,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>93</v>
       </c>
@@ -1413,7 +1407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1432,7 +1426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1685,7 +1679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>71</v>
       </c>
@@ -1698,7 +1692,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>72</v>
       </c>
@@ -1749,7 +1743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
@@ -1762,7 +1756,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>73</v>
       </c>
@@ -1896,7 +1890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
@@ -1972,7 +1966,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>76</v>
       </c>
@@ -1985,7 +1979,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2172,7 +2166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>92</v>
       </c>
@@ -2185,7 +2179,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>77</v>
       </c>
@@ -2223,7 +2217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>78</v>
       </c>
@@ -2416,7 +2410,7 @@
         <v>8</v>
       </c>
       <c r="I66" s="1" t="str">
-        <f t="shared" ref="I66:I97" si="2">IF(H66="x",$H$1,IF(G66="x",$G$1,IF(F66="x",$F$1,IF(E66="x",$E$1,IF(D66="x",$D$1,IF(C66="x",$C$1,IF(B66="x",$B$1,"???")))))))</f>
+        <f t="shared" ref="I66:I79" si="2">IF(H66="x",$H$1,IF(G66="x",$G$1,IF(F66="x",$F$1,IF(E66="x",$E$1,IF(D66="x",$D$1,IF(C66="x",$C$1,IF(B66="x",$B$1,"???")))))))</f>
         <v>Custom DBC
 (Patch-Z)</v>
       </c>
@@ -2443,7 +2437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>88</v>
       </c>
@@ -2456,7 +2450,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>89</v>
       </c>
@@ -2469,7 +2463,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>90</v>
       </c>
@@ -2482,7 +2476,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>64</v>
       </c>
@@ -2493,6 +2487,9 @@
         <f t="shared" si="2"/>
         <v>Custom DBC
 (Patch-Z)</v>
+      </c>
+      <c r="J71" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2514,7 +2511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>84</v>
       </c>
@@ -2527,7 +2524,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>83</v>
       </c>
@@ -2540,7 +2537,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>82</v>
       </c>
@@ -2553,7 +2550,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>81</v>
       </c>
@@ -2566,7 +2563,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>91</v>
       </c>
@@ -2579,7 +2576,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
@@ -2592,7 +2589,7 @@
 (Patch-5)</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>79</v>
       </c>
